--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/updateMember-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/updateMember-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="108">
-  <si>
-    <t>Statement: user-controller.updateMember(memberId, data) – Server Action. Validates UpdateMemberInput (all fields optional). Delegates to userService.updateMember(). Returns ActionResult&lt;MemberWithUser&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="174">
+  <si>
+    <t>Statement: updateMember(id, data) – Validates the update-member input and returns an ActionResult&lt;MemberWithUser&gt;. Returns success with the updated member on success. Returns a field-level validation error for schema failures without calling the service. An empty update object is accepted and returns success. Returns a failure with the service error message for NotFoundError, ConflictError, and TransactionError.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, data: UpdateMemberInput (all optional)</t>
+    <t>Input: id: string, data: UpdateMemberInput { email?, fullName?, phone?, dateOfBirth?, password?, membershipStart? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userService.updateMember is mock-injected</t>
+    <t>The member store may be empty or populated. All fields in UpdateMemberInput are optional. When a field is present, it must pass the same format and length rules as in createMember. When a field is undefined, it is ignored and the update proceeds. An empty object is valid.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;MemberWithUser&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;MemberWithUser&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: updated MemberWithUser returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: member updated successfully, returned data reflects the applied changes. On validation failure: field-level validation error returned, the service is not called. On service error: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,43 +64,34 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>all fields valid</t>
-  </si>
-  <si>
-    <t>optional fields pass schema</t>
-  </si>
-  <si>
-    <t>fullName optional</t>
-  </si>
-  <si>
-    <t>fullName ≥ 8 chars if provided</t>
-  </si>
-  <si>
-    <t>fullName &lt; 8 chars → validation error</t>
-  </si>
-  <si>
-    <t>email optional</t>
-  </si>
-  <si>
-    <t>valid email if provided</t>
-  </si>
-  <si>
-    <t>invalid email if provided → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves updated MemberWithUser</t>
-  </si>
-  <si>
-    <t>throws NotFoundError → failure with message</t>
-  </si>
-  <si>
-    <t>throws ConflictError → failure with message</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>Valid partial input ({ fullName: "Updated Name" }), matching member exists → member updated successfully, returned fullName matches the new value</t>
+  </si>
+  <si>
+    <t>Empty update object ({}) → member updated successfully</t>
+  </si>
+  <si>
+    <t>Email format</t>
+  </si>
+  <si>
+    <t>Invalid email value ("bad") → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>ID existence</t>
+  </si>
+  <si>
+    <t>Non-existent id, no matching record exists (NotFoundError) → operation fails with the returned error message</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>The provided email is already registered to another account (ConflictError) → operation fails with the returned error message</t>
+  </si>
+  <si>
+    <t>A database transaction failure occurs (TransactionError) → operation fails with the returned error message</t>
   </si>
   <si>
     <t>No TC</t>
@@ -120,55 +109,61 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,2,4,6</t>
-  </si>
-  <si>
-    <t>{ fullName: "John Updated Doe" }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ fullName: "Jo" }</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ email: "bad-email" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>valid update, service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Member not found" }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>valid update, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Email already in use" }</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid update, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: "Updated Name" }, member exists and is updated successfully</t>
+  </si>
+  <si>
+    <t>member updated successfully, returned data fullName is "Updated Name"</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>known existing member id, data: {} (empty update object)</t>
+  </si>
+  <si>
+    <t>member updated successfully</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { email: "bad" }</t>
+  </si>
+  <si>
+    <t>validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>non-existent id, data: { fullName: "Updated Name" }, no matching record exists (NotFoundError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "Not found"</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { email: "taken@example.com" }, email already registered (ConflictError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "Email taken"</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: "Updated Name" }, database transaction failure occurs (TransactionError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "DB failure"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -177,58 +172,259 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>fullName length boundary</t>
-  </si>
-  <si>
-    <t>fullName 7 chars → invalid</t>
-  </si>
-  <si>
-    <t>fullName 8 chars → valid</t>
-  </si>
-  <si>
-    <t>fullName boundary interior</t>
-  </si>
-  <si>
-    <t>fullName 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>fullName 63 chars → valid (max-1)</t>
+    <t>id boundary</t>
+  </si>
+  <si>
+    <t>id: "" (empty string, length 0): no record can match → operation fails</t>
+  </si>
+  <si>
+    <t>id: "a" (one character), no matching record exists → operation fails</t>
+  </si>
+  <si>
+    <t>id: "a" (one character), matching record exists → member updated successfully</t>
+  </si>
+  <si>
+    <t>fullName length</t>
+  </si>
+  <si>
+    <t>fullName: 8 characters (minimum valid length) → member updated successfully</t>
+  </si>
+  <si>
+    <t>password length</t>
+  </si>
+  <si>
+    <t>password: 64 characters meeting all rules (maximum valid length) → member updated successfully</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email: undefined (field omitted) → update proceeds successfully, email not changed</t>
+  </si>
+  <si>
+    <t>email: "" (empty string) → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>email: "a" (one character, invalid format) → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>fullName presence</t>
+  </si>
+  <si>
+    <t>fullName: undefined (field omitted) → update proceeds successfully, fullName not changed</t>
+  </si>
+  <si>
+    <t>fullName: "" (empty string) → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>fullName: "a" (one character, below minimum) → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>phone presence</t>
+  </si>
+  <si>
+    <t>phone: undefined (field omitted) → update proceeds successfully, phone not changed</t>
+  </si>
+  <si>
+    <t>phone: "" (empty string) → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>phone: "a" (one character, invalid format) → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth presence</t>
+  </si>
+  <si>
+    <t>dateOfBirth: undefined (field omitted) → update proceeds successfully, dateOfBirth not changed</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "" (empty string) → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "a" (one character, invalid format) → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>password presence</t>
+  </si>
+  <si>
+    <t>password: undefined (field omitted) → update proceeds successfully, password not changed</t>
+  </si>
+  <si>
+    <t>password: "" (empty string) → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>password: "a" (one character, fails all rules) → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>membershipStart presence</t>
+  </si>
+  <si>
+    <t>membershipStart: undefined (field omitted) → update proceeds successfully, membershipStart not changed</t>
+  </si>
+  <si>
+    <t>membershipStart: "" (empty string) → validation fails: membershipStart field error returned</t>
+  </si>
+  <si>
+    <t>membershipStart: "a" (one character, invalid format) → validation fails: membershipStart field error returned</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>fullName=7</t>
-  </si>
-  <si>
-    <t>{ fullName: "1234567" }</t>
-  </si>
-  <si>
-    <t>success=false, errors.fullName defined</t>
-  </si>
-  <si>
-    <t>fullName=8</t>
-  </si>
-  <si>
-    <t>{ fullName: "12345678" }</t>
-  </si>
-  <si>
-    <t>schema passes</t>
-  </si>
-  <si>
-    <t>fullName=9</t>
-  </si>
-  <si>
-    <t>{ fullName: "John Doe1" }</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>fullName=63</t>
-  </si>
-  <si>
-    <t>{ fullName: "C".repeat(63) }</t>
+    <t>BVA-1  (id="")</t>
+  </si>
+  <si>
+    <t>id: "", data: { fullName: "Updated Name" }, no record can match an empty id</t>
+  </si>
+  <si>
+    <t>BVA-2  (id="a", no match)</t>
+  </si>
+  <si>
+    <t>id: "a", data: { fullName: "Updated Name" }, no member exists with id "a"</t>
+  </si>
+  <si>
+    <t>BVA-3  (id="a", match)</t>
+  </si>
+  <si>
+    <t>id: "a", data: { fullName: "Updated Name" }, a member with id "a" exists in the store</t>
+  </si>
+  <si>
+    <t>member updated successfully, returned data id is "a"</t>
+  </si>
+  <si>
+    <t>BVA-4  (fullName=8 chars)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: "A".repeat(8) }</t>
+  </si>
+  <si>
+    <t>BVA-5  (password=64 chars)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { password: "P1@" + "a".repeat(61) }</t>
+  </si>
+  <si>
+    <t>BVA-6  (email=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { email: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-7  (email="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { email: "" }</t>
+  </si>
+  <si>
+    <t>BVA-8  (email="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { email: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-9  (fullName=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-10 (fullName="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>BVA-11 (fullName="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { fullName: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-12 (phone=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { phone: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-13 (phone="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { phone: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>BVA-14 (phone="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { phone: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-15 (dateOfBirth=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { dateOfBirth: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-16 (dateOfBirth="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { dateOfBirth: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>BVA-17 (dateOfBirth="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { dateOfBirth: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-18 (password=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { password: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-19 (password="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { password: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>BVA-20 (password="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { password: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-21 (membershipStart=undefined)</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { membershipStart: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-22 (membershipStart="")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { membershipStart: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: membershipStart field error returned</t>
+  </si>
+  <si>
+    <t>BVA-23 (membershipStart="a")</t>
+  </si>
+  <si>
+    <t>known existing member id, data: { membershipStart: "a" }</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -237,70 +433,73 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>Valid update, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, MemberWithUser returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>fullName 7 chars</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid email</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws ConflictError</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>fullName 9 chars</t>
-  </si>
-  <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>fullName 63 chars</t>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
+  </si>
+  <si>
+    <t>BVA-20</t>
+  </si>
+  <si>
+    <t>BVA-21</t>
+  </si>
+  <si>
+    <t>BVA-22</t>
+  </si>
+  <si>
+    <t>BVA-23</t>
   </si>
   <si>
     <t>Testing</t>
@@ -333,16 +532,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-05</t>
+    <t>CTRL-09</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -858,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -899,10 +1095,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -913,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -930,10 +1126,10 @@
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -941,13 +1137,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,55 +1151,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1026,19 +1180,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1046,16 +1200,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1063,16 +1217,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1080,16 +1234,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1097,16 +1251,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1114,16 +1268,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1131,16 +1285,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1151,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1161,13 +1315,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1175,43 +1329,252 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1234,19 +1597,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1254,16 +1617,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1271,16 +1634,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1288,16 +1651,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1305,16 +1668,339 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>67</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1325,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1338,22 +2024,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1381,19 +2067,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1401,19 +2087,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1421,19 +2107,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1441,19 +2127,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1461,19 +2147,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,16 +2170,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,16 +2190,436 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>67</v>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1541,16 +2647,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1558,45 +2664,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>104</v>
+      <c r="A3" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="1">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1605,19 +2711,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>107</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
